--- a/housecall-pricebook/foxfern_pricing_calculator.xlsx
+++ b/housecall-pricebook/foxfern_pricing_calculator.xlsx
@@ -612,7 +612,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Interior Remodeling Labor</t>
+          <t>Residential Interior Remodeling Labor</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -648,7 +648,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Exterior Remodeling Labor</t>
+          <t>Residential Exterior Remodeling Labor</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -684,7 +684,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Handyman Labor</t>
+          <t>Residential Handyman Labor</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -720,7 +720,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Concrete &amp; Hardscape Labor</t>
+          <t>Residential Concrete &amp; Hardscape Labor</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -756,7 +756,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Demolition &amp; Haul-Away Labor</t>
+          <t>Residential Demolition &amp; Haul-Away Labor</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -985,7 +985,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Interior Remodeling Labor</t>
+          <t>Residential Interior Remodeling Labor</t>
         </is>
       </c>
       <c r="B4" s="10" t="n">
@@ -1003,7 +1003,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Exterior Remodeling Labor</t>
+          <t>Residential Exterior Remodeling Labor</t>
         </is>
       </c>
       <c r="B5" s="10" t="n">
@@ -1021,7 +1021,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Handyman Labor</t>
+          <t>Residential Handyman Labor</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
@@ -1039,7 +1039,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Concrete &amp; Hardscape Labor</t>
+          <t>Residential Concrete &amp; Hardscape Labor</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
@@ -1057,7 +1057,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Demolition &amp; Haul-Away Labor</t>
+          <t>Residential Demolition &amp; Haul-Away Labor</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
